--- a/reports/集团总公司_利润表_2026-06.xlsx
+++ b/reports/集团总公司_利润表_2026-06.xlsx
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>232890515</v>
+        <v>253677759</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>177068363</v>
+        <v>192396561</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>975333309</v>
+        <v>1060632675</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2100,10 +2100,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>721249</v>
+        <v>929621</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4076896</v>
+        <v>5277689</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2128,10 +2128,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>627454</v>
+        <v>813603</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>3536834</v>
+        <v>4615984</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2156,10 +2156,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>530140</v>
+        <v>687410</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>2996889</v>
+        <v>3894983</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2184,10 +2184,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>486965</v>
+        <v>635447</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>2757625</v>
+        <v>3594088</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2212,10 +2212,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>265576</v>
+        <v>350142</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1498834</v>
+        <v>1976283</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2240,10 +2240,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>212552</v>
+        <v>276325</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1198822</v>
+        <v>1556978</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>230046579</v>
+        <v>249985211</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>174224427</v>
+        <v>188704013</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>89673307</v>
+        <v>98590143</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>481827564</v>
+        <v>529420931</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1644714</v>
+        <v>2924552</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>9290929</v>
+        <v>16491777</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1481442</v>
+        <v>2125521</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>8392327</v>
+        <v>11997605</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>79655759</v>
+        <v>83755663</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>449743605</v>
+        <v>474220833</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1704582</v>
+        <v>2116577</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>9590751</v>
+        <v>12003340</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>741340</v>
+        <v>1057153</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4195462</v>
+        <v>5999873</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2489,10 +2489,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2642513</v>
+        <v>3166848</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>14988785</v>
+        <v>17995534</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2517,10 +2517,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1169420</v>
+        <v>1584656</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>6594815</v>
+        <v>8994559</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>55646200</v>
+        <v>55484078</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>313435395</v>
+        <v>313121534</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>175952</v>
+        <v>174909</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1041300</v>
+        <v>1049945</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>3370946</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>19046088</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2629,10 +2629,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>2251265</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>12695585</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>168548047</v>
+        <v>191133891</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>135272313</v>
+        <v>143026106</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>106390489</v>
+        <v>114246943</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>600452337</v>
+        <v>642088805</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2737,10 +2737,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>28881824</v>
+        <v>28779163</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>162426412</v>
+        <v>162643107</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2765,10 +2765,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>5639707</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>31784641</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1802064</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>10174630</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>1124332</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>6360502</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1346898</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>7632919</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -2877,10 +2877,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>1008785</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>5723899</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -2905,10 +2905,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>671987</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3814811</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -2933,10 +2933,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>559945</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>3177747</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -2961,10 +2961,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>3124246</v>
+        <v>3121053</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>17680029</v>
+        <v>17676026</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -2989,10 +2989,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1471016</v>
+        <v>1468581</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>8333155</v>
+        <v>8329562</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3017,10 +3017,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>3832464</v>
+        <v>3829098</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>21585506</v>
+        <v>21557602</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3045,10 +3045,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>24790161</v>
+        <v>24806293</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>145182879</v>
+        <v>145139065</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>365853</v>
+        <v>3039452</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2125844</v>
+        <v>17079664</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>1163010</v>
+        <v>1158171</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>6858508</v>
+        <v>6917160</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3129,10 +3129,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>1211817</v>
+        <v>1105627</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>7094422</v>
+        <v>6609452</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3157,10 +3157,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>125129</v>
+        <v>124099</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>732173</v>
+        <v>741439</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3185,10 +3185,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>492707</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2948653</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>985285</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>5564458</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>327398</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1966953</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3269,10 +3269,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>245136</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1475351</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>408026</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>2458731</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3325,10 +3325,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1399898</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>7947142</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3353,10 +3353,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>217465</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1310563</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3381,10 +3381,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>163220</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>982528</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3409,10 +3409,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>272397</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1636915</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>191001</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1145493</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3465,10 +3465,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>136667</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>818074</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>109498</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>654462</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3521,10 +3521,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>82205</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>490930</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3549,7 +3549,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>61498532</v>
+        <v>62272956</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>66538874</v>
+        <v>66631891</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3601,10 +3601,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>563775</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>3178793</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3629,10 +3629,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>136625</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>819396</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>218825</v>
+        <v>216158</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1282671</v>
+        <v>1298955</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>61279707</v>
+        <v>62620573</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>7406646</v>
+        <v>7287568</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>43367577</v>
+        <v>43917537</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3739,7 +3739,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>53873061</v>
+        <v>55333005</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -3789,7 +3789,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>53873061</v>
+        <v>55333005</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>53873061</v>
+        <v>55333005</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>53873061</v>
+        <v>55333005</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4067,7 +4067,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>53873061</v>
+        <v>55333005</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
